--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_FUNDACION GLOBALCAJA LA RODA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_FUNDACION GLOBALCAJA LA RODA.xlsx
@@ -565,67 +565,67 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4631</v>
+        <v>5.382700000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5517</v>
+        <v>4.1613</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9114</v>
+        <v>1.2213</v>
       </c>
       <c r="G2" t="n">
-        <v>6.7174</v>
+        <v>6.5932</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2846000000000002</v>
+        <v>-0.4435</v>
       </c>
       <c r="I2" t="n">
-        <v>7.002</v>
+        <v>7.0367</v>
       </c>
       <c r="J2" t="n">
-        <v>6.1178</v>
+        <v>6.4518</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.6525000000000001</v>
+        <v>-0.5438</v>
       </c>
       <c r="L2" t="n">
-        <v>6.7705</v>
+        <v>6.9956</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5996000000000002</v>
+        <v>0.1413000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>0.368</v>
+        <v>0.1003000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2315999999999999</v>
+        <v>0.04110000000000014</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4000999999999999</v>
+        <v>0.3895</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.2013</v>
+        <v>-4.0895</v>
       </c>
       <c r="R2" t="n">
-        <v>4.6013</v>
+        <v>4.4789</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5345</v>
+        <v>-1.4778</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6841000000000002</v>
+        <v>-0.5914999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8503000000000001</v>
+        <v>-0.8863000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1200000000000001</v>
+        <v>-0.1221</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3193</v>
+        <v>2.3906</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.4393</v>
+        <v>-2.5127</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5299</v>
+        <v>2.5461</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.1762</v>
+        <v>-0.5211000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>3.706</v>
+        <v>3.0671</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8018000000000001</v>
+        <v>0.8345000000000002</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.03989999999999999</v>
+        <v>-0.0411</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8418000000000001</v>
+        <v>0.8755000000000002</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.4921</v>
+        <v>-0.09499999999999997</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2125000000000001</v>
+        <v>0.4389</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.7047000000000001</v>
+        <v>-0.5339</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2939</v>
+        <v>0.9295</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2527</v>
+        <v>-0.4800999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5465</v>
+        <v>1.4094</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.8002</v>
+        <v>-0.779</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.2012</v>
+        <v>-4.0895</v>
       </c>
       <c r="R3" t="n">
-        <v>3.401</v>
+        <v>3.3105</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1084</v>
+        <v>1.0605</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.001900000000000013</v>
+        <v>0.05179999999999996</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1104</v>
+        <v>1.0088</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4199</v>
+        <v>1.4301</v>
       </c>
       <c r="W3" t="n">
-        <v>3.5191</v>
+        <v>3.6116</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.0991</v>
+        <v>-2.1816</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. CASTELANOS POLA</t>
+          <t>J. KELLIER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1085</v>
+        <v>2.3451</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6012</v>
+        <v>2.7408</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4926</v>
+        <v>-0.3956999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.2841</v>
+        <v>-0.101</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.8628</v>
+        <v>6.563199999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4212</v>
+        <v>-6.6642</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1545</v>
+        <v>3.8801</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3691</v>
+        <v>7.3564</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5236</v>
+        <v>-3.4762</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.4386</v>
+        <v>-3.9811</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4938</v>
+        <v>-0.7932000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.9448</v>
+        <v>-3.1879</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8005</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-6.2316</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8005</v>
+        <v>4.0895</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9118</v>
+        <v>2.0188</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7273000000000001</v>
+        <v>1.1796</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1845</v>
+        <v>0.8391000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6802</v>
+        <v>2.5694</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7194</v>
+        <v>3.9126</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0392</v>
+        <v>-1.3432</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. KELLIER</t>
+          <t>A. CASTELANOS POLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0929</v>
+        <v>1.9735</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7294</v>
+        <v>3.9388</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3635000000000002</v>
+        <v>-1.9652</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1132</v>
+        <v>-2.3202</v>
       </c>
       <c r="H5" t="n">
-        <v>6.4546</v>
+        <v>-1.8304</v>
       </c>
       <c r="I5" t="n">
-        <v>-6.5678</v>
+        <v>-0.4899</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3645</v>
+        <v>1.3992</v>
       </c>
       <c r="K5" t="n">
-        <v>6.950699999999999</v>
+        <v>-0.1897</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.5861</v>
+        <v>1.5889</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.4777</v>
+        <v>-3.7195</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4960999999999999</v>
+        <v>-1.6407</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.9817</v>
+        <v>-2.0788</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.2007</v>
+        <v>1.7526</v>
       </c>
       <c r="Q5" t="n">
-        <v>-6.401899999999999</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>4.2012</v>
+        <v>1.7526</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0896</v>
+        <v>1.8791</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1297</v>
+        <v>0.7595000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9599</v>
+        <v>1.1195</v>
       </c>
       <c r="V5" t="n">
-        <v>2.3173</v>
+        <v>0.6621</v>
       </c>
       <c r="W5" t="n">
-        <v>3.637</v>
+        <v>1.78</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3198</v>
+        <v>-1.118</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.8563000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3248</v>
+        <v>3.732200000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.4684</v>
+        <v>-2.8759</v>
       </c>
       <c r="G6" t="n">
-        <v>4.8649</v>
+        <v>4.849299999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0254</v>
+        <v>1.9719</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8396</v>
+        <v>2.8774</v>
       </c>
       <c r="J6" t="n">
-        <v>7.2463</v>
+        <v>7.4636</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6413</v>
+        <v>1.7165</v>
       </c>
       <c r="L6" t="n">
-        <v>5.6049</v>
+        <v>5.747</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.3815</v>
+        <v>-2.6143</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3839</v>
+        <v>0.2554</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.7653</v>
+        <v>-2.8696</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.401</v>
+        <v>-3.3106</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.0015</v>
+        <v>-4.868399999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6319</v>
+        <v>0.6090000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1198</v>
+        <v>-0.08390000000000003</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7518</v>
+        <v>0.6930000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2395</v>
+        <v>-1.2916</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1998</v>
+        <v>1.221</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4392</v>
+        <v>-2.5126</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3377999999999997</v>
+        <v>0.3404000000000003</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7679</v>
+        <v>2.4706</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4301</v>
+        <v>-2.1302</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0253</v>
+        <v>1.9589</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4512</v>
+        <v>-1.6222</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4765</v>
+        <v>3.5812</v>
       </c>
       <c r="J7" t="n">
-        <v>4.5675</v>
+        <v>5.0019</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.01280000000000014</v>
+        <v>0.113</v>
       </c>
       <c r="L7" t="n">
-        <v>4.5804</v>
+        <v>4.8889</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.5422</v>
+        <v>-3.043</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4384</v>
+        <v>-1.7353</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1038</v>
+        <v>-1.3076</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.401</v>
+        <v>-3.3106</v>
       </c>
       <c r="R7" t="n">
-        <v>3.801</v>
+        <v>3.7</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.0072</v>
+        <v>-1.9566</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.7179</v>
+        <v>-1.6113</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2894</v>
+        <v>-0.3452999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.08030000000000004</v>
+        <v>-0.05160000000000009</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3193</v>
+        <v>2.3905</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.3995</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="8">
@@ -1033,64 +1033,64 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6665</v>
+        <v>-0.7206</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6575</v>
+        <v>1.9405</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3239</v>
+        <v>-2.6611</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3916</v>
+        <v>2.2015</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9994000000000001</v>
+        <v>0.8809</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3922</v>
+        <v>1.3207</v>
       </c>
       <c r="J8" t="n">
-        <v>4.8809</v>
+        <v>4.996</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0794</v>
+        <v>2.1347</v>
       </c>
       <c r="L8" t="n">
-        <v>2.8015</v>
+        <v>2.8613</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4893</v>
+        <v>-2.7944</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.08</v>
+        <v>-1.2538</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4093</v>
+        <v>-1.5406</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.2004</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6972</v>
+        <v>-1.6506</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8623</v>
+        <v>-0.8103</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8349</v>
+        <v>-0.8403</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1606000000000001</v>
+        <v>-0.1031</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.1606000000000001</v>
+        <v>-0.1031</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.1959</v>
+        <v>-6.3751</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.5405</v>
+        <v>-5.2773</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6552999999999998</v>
+        <v>-1.0977</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8820999999999999</v>
+        <v>-1.0561</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4844</v>
+        <v>1.3283</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.3666</v>
+        <v>-2.3845</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5485</v>
+        <v>-1.4223</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8798</v>
+        <v>0.9032</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.4282</v>
+        <v>-2.3255</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6662999999999999</v>
+        <v>0.3662000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6047</v>
+        <v>0.4252000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06170000000000009</v>
+        <v>-0.05899999999999994</v>
       </c>
       <c r="P9" t="n">
-        <v>9.999999999987796e-05</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2007</v>
+        <v>2.1421</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.2145</v>
+        <v>-3.1373</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.7914</v>
+        <v>-1.7129</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.4231</v>
+        <v>-1.4244</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.0992</v>
+        <v>-2.1816</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.0992</v>
+        <v>-2.1816</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.6669</v>
+        <v>-7.4103</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2074</v>
+        <v>-2.568000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.4596</v>
+        <v>-4.8422</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.3658</v>
+        <v>-4.277</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.337</v>
+        <v>-0.2262</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.0288</v>
+        <v>-4.0508</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1341</v>
+        <v>0.2595</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6143</v>
+        <v>0.8829</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7485000000000001</v>
+        <v>-0.6234000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.2316</v>
+        <v>-4.5366</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9512999999999999</v>
+        <v>-1.1091</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.2803</v>
+        <v>-3.4275</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6005</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.201</v>
+        <v>-3.1158</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6004</v>
+        <v>1.5579</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.8201</v>
+        <v>-2.7449</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.1915</v>
+        <v>-2.1024</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6286</v>
+        <v>-0.6425000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>1.1195</v>
+        <v>1.1694</v>
       </c>
       <c r="W10" t="n">
-        <v>2.3193</v>
+        <v>2.3905</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-11.5399</v>
+        <v>-11.439</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.1073</v>
+        <v>-9.6416</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4326</v>
+        <v>-1.7974</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.2377</v>
+        <v>-3.2482</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8165</v>
+        <v>-1.7451</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4211</v>
+        <v>-1.5031</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.907</v>
+        <v>-0.7141999999999998</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.187</v>
+        <v>-0.9978000000000002</v>
       </c>
       <c r="L11" t="n">
-        <v>0.28</v>
+        <v>0.2838</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.3307</v>
+        <v>-2.534</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.7473</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.7011</v>
+        <v>-1.7867</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.402100000000001</v>
+        <v>-7.2052</v>
       </c>
       <c r="Q11" t="n">
-        <v>-9.2026</v>
+        <v>-8.9579</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8005</v>
+        <v>1.7527</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8192999999999999</v>
+        <v>0.7945</v>
       </c>
       <c r="T11" t="n">
-        <v>0.002400000000000013</v>
+        <v>0.03060000000000002</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8169</v>
+        <v>0.7639</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.7194</v>
+        <v>-1.7801</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7194</v>
+        <v>-1.7801</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.6806</v>
+        <v>-12.5009</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.398899999999999</v>
+        <v>0.9761999999999986</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.281599999999997</v>
+        <v>-13.477</v>
       </c>
       <c r="G12" t="n">
-        <v>5.918099999999999</v>
+        <v>5.434899999999996</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1718</v>
+        <v>4.835799999999998</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7465999999999999</v>
+        <v>0.5990000000000011</v>
       </c>
       <c r="J12" t="n">
-        <v>24.2498</v>
+        <v>27.2206</v>
       </c>
       <c r="K12" t="n">
-        <v>10.1566</v>
+        <v>11.8143</v>
       </c>
       <c r="L12" t="n">
-        <v>14.0934</v>
+        <v>15.4065</v>
       </c>
       <c r="M12" t="n">
-        <v>-18.3318</v>
+        <v>-21.7859</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.9852</v>
+        <v>-6.978599999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-13.3465</v>
+        <v>-14.8072</v>
       </c>
       <c r="P12" t="n">
-        <v>-14.0041</v>
+        <v>-13.6316</v>
       </c>
       <c r="Q12" t="n">
-        <v>-40.0117</v>
+        <v>-38.9475</v>
       </c>
       <c r="R12" t="n">
-        <v>26.0074</v>
+        <v>25.3158</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.712499999999999</v>
+        <v>-4.6053</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.509500000000001</v>
+        <v>-4.8908</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7971999999999997</v>
+        <v>0.2855000000000003</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1178999999999997</v>
+        <v>0.3008999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>16.8726</v>
+        <v>17.5937</v>
       </c>
       <c r="X12" t="n">
-        <v>-16.7545</v>
+        <v>-17.293</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_FUNDACION GLOBALCAJA LA RODA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_FUNDACION GLOBALCAJA LA RODA.xlsx
@@ -565,13 +565,13 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.382700000000001</v>
+        <v>6.6889</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1613</v>
+        <v>4.4225</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2213</v>
+        <v>2.2663</v>
       </c>
       <c r="G2" t="n">
         <v>6.5932</v>
@@ -610,13 +610,13 @@
         <v>4.4789</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4778</v>
+        <v>-0.1717000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5914999999999999</v>
+        <v>-0.3304000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8863000000000001</v>
+        <v>0.1586</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1221</v>
@@ -643,13 +643,13 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5461</v>
+        <v>2.7436</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5211000000000001</v>
+        <v>-0.0605</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0671</v>
+        <v>2.8042</v>
       </c>
       <c r="G3" t="n">
         <v>0.8345000000000002</v>
@@ -688,13 +688,13 @@
         <v>3.3105</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0605</v>
+        <v>1.2582</v>
       </c>
       <c r="T3" t="n">
-        <v>0.05179999999999996</v>
+        <v>0.5122</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0088</v>
+        <v>0.7459</v>
       </c>
       <c r="V3" t="n">
         <v>1.4301</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. KELLIER</t>
+          <t>N. CEBRIAN HERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3451</v>
+        <v>1.606</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7408</v>
+        <v>3.192200000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3956999999999999</v>
+        <v>-1.5862</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.101</v>
+        <v>1.9589</v>
       </c>
       <c r="H4" t="n">
-        <v>6.563199999999999</v>
+        <v>-1.6222</v>
       </c>
       <c r="I4" t="n">
-        <v>-6.6642</v>
+        <v>3.5812</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8801</v>
+        <v>5.0019</v>
       </c>
       <c r="K4" t="n">
-        <v>7.3564</v>
+        <v>0.113</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.4762</v>
+        <v>4.8889</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.9811</v>
+        <v>-3.043</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7932000000000001</v>
+        <v>-1.7353</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.1879</v>
+        <v>-1.3076</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.1421</v>
+        <v>0.3895</v>
       </c>
       <c r="Q4" t="n">
-        <v>-6.2316</v>
+        <v>-3.3106</v>
       </c>
       <c r="R4" t="n">
-        <v>4.0895</v>
+        <v>3.7</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0188</v>
+        <v>-0.6908</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1796</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8391000000000001</v>
+        <v>0.1988</v>
       </c>
       <c r="V4" t="n">
-        <v>2.5694</v>
+        <v>-0.05160000000000009</v>
       </c>
       <c r="W4" t="n">
-        <v>3.9126</v>
+        <v>2.3905</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.3432</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9735</v>
+        <v>1.5083</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9388</v>
+        <v>3.3407</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9652</v>
+        <v>-1.8324</v>
       </c>
       <c r="G5" t="n">
         <v>-2.3202</v>
@@ -844,13 +844,13 @@
         <v>1.7526</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8791</v>
+        <v>1.4139</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7595000000000001</v>
+        <v>0.1615</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1195</v>
+        <v>1.2524</v>
       </c>
       <c r="V5" t="n">
         <v>0.6621</v>
@@ -877,13 +877,13 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8563000000000001</v>
+        <v>0.5456000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>3.732200000000001</v>
+        <v>3.5948</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.8759</v>
+        <v>-3.0492</v>
       </c>
       <c r="G6" t="n">
         <v>4.849299999999999</v>
@@ -922,13 +922,13 @@
         <v>1.5579</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6090000000000001</v>
+        <v>0.2983</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.08390000000000003</v>
+        <v>-0.2215</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6930000000000001</v>
+        <v>0.5198</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2916</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. CEBRIAN HERNANDEZ</t>
+          <t>J. KELLIER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3404000000000003</v>
+        <v>0.5088999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4706</v>
+        <v>1.6683</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1302</v>
+        <v>-1.1594</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9589</v>
+        <v>-0.101</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6222</v>
+        <v>6.563199999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5812</v>
+        <v>-6.6642</v>
       </c>
       <c r="J7" t="n">
-        <v>5.0019</v>
+        <v>3.8801</v>
       </c>
       <c r="K7" t="n">
-        <v>0.113</v>
+        <v>7.3564</v>
       </c>
       <c r="L7" t="n">
-        <v>4.8889</v>
+        <v>-3.4762</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.043</v>
+        <v>-3.9811</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7353</v>
+        <v>-0.7932000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3076</v>
+        <v>-3.1879</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3895</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.3106</v>
+        <v>-6.2316</v>
       </c>
       <c r="R7" t="n">
-        <v>3.7</v>
+        <v>4.0895</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.9566</v>
+        <v>0.1824</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.6113</v>
+        <v>0.1071</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3452999999999999</v>
+        <v>0.07540000000000002</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.05160000000000009</v>
+        <v>2.5694</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3905</v>
+        <v>3.9126</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.4421</v>
+        <v>-1.3432</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7206</v>
+        <v>-0.2083</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9405</v>
+        <v>1.9026</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6611</v>
+        <v>-2.1108</v>
       </c>
       <c r="G8" t="n">
         <v>2.2015</v>
@@ -1078,13 +1078,13 @@
         <v>0.9737</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6506</v>
+        <v>-1.1382</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8103</v>
+        <v>-0.8482000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8403</v>
+        <v>-0.29</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1031</v>
@@ -1111,13 +1111,13 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.3751</v>
+        <v>-5.113799999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.2773</v>
+        <v>-4.7549</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0977</v>
+        <v>-0.3588999999999998</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0561</v>
@@ -1156,13 +1156,13 @@
         <v>2.1421</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.1373</v>
+        <v>-1.8761</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.7129</v>
+        <v>-1.1905</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.4244</v>
+        <v>-0.6856</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1816</v>
@@ -1189,13 +1189,13 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.4103</v>
+        <v>-6.428900000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.568000000000001</v>
+        <v>-1.97</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.8422</v>
+        <v>-4.4588</v>
       </c>
       <c r="G10" t="n">
         <v>-4.277</v>
@@ -1234,13 +1234,13 @@
         <v>1.5579</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.7449</v>
+        <v>-1.7635</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.1024</v>
+        <v>-1.5044</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6425000000000001</v>
+        <v>-0.2592</v>
       </c>
       <c r="V10" t="n">
         <v>1.1694</v>
@@ -1267,13 +1267,13 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-11.439</v>
+        <v>-11.7397</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.6416</v>
+        <v>-9.741199999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7974</v>
+        <v>-1.9984</v>
       </c>
       <c r="G11" t="n">
         <v>-3.2482</v>
@@ -1312,13 +1312,13 @@
         <v>1.7527</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7945</v>
+        <v>0.4938</v>
       </c>
       <c r="T11" t="n">
-        <v>0.03060000000000002</v>
+        <v>-0.06920000000000004</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7639</v>
+        <v>0.5629</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7801</v>
@@ -1345,16 +1345,16 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.5009</v>
+        <v>-9.889399999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9761999999999986</v>
+        <v>1.5945</v>
       </c>
       <c r="F12" t="n">
-        <v>-13.477</v>
+        <v>-11.4836</v>
       </c>
       <c r="G12" t="n">
-        <v>5.434899999999996</v>
+        <v>5.4349</v>
       </c>
       <c r="H12" t="n">
         <v>4.835799999999998</v>
@@ -1375,7 +1375,7 @@
         <v>-21.7859</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.978599999999999</v>
+        <v>-6.9786</v>
       </c>
       <c r="O12" t="n">
         <v>-14.8072</v>
@@ -1390,16 +1390,16 @@
         <v>25.3158</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.6053</v>
+        <v>-1.9937</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.8908</v>
+        <v>-4.273000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2855000000000003</v>
+        <v>2.279</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3008999999999999</v>
+        <v>0.3009000000000004</v>
       </c>
       <c r="W12" t="n">
         <v>17.5937</v>
